--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_60/per_file_predictions_epoch_60.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_60/per_file_predictions_epoch_60.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8917,0.0892,0.0174,0.0009</t>
-  </si>
-  <si>
-    <t>0.9794,0.0042,0.0023,0.0023</t>
-  </si>
-  <si>
-    <t>0.9836,0.0097,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9740,0.0150,0.0024,0.0006</t>
-  </si>
-  <si>
-    <t>0.9729,0.0264,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9631,0.0386,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9566,0.0323,0.0028,0.0011</t>
-  </si>
-  <si>
-    <t>0.9019,0.0866,0.0046,0.0018</t>
-  </si>
-  <si>
-    <t>0.8242,0.1828,0.0217,0.0041</t>
-  </si>
-  <si>
-    <t>0.8923,0.0970,0.0022,0.0011</t>
-  </si>
-  <si>
-    <t>0.9597,0.0382,0.0016,0.0005</t>
-  </si>
-  <si>
-    <t>0.9653,0.0287,0.0010,0.0005</t>
-  </si>
-  <si>
-    <t>0.9876,0.0036,0.0035,0.0002</t>
-  </si>
-  <si>
-    <t>0.9235,0.0180,0.0431,0.0006</t>
-  </si>
-  <si>
-    <t>0.8306,0.0309,0.1586,0.0013</t>
-  </si>
-  <si>
-    <t>0.7720,0.0108,0.4388,0.0007</t>
-  </si>
-  <si>
-    <t>0.9838,0.0101,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.7316,0.4480,0.0027,0.0001</t>
-  </si>
-  <si>
-    <t>0.6595,0.5273,0.0054,0.0002</t>
-  </si>
-  <si>
-    <t>0.9460,0.0623,0.0026,0.0004</t>
-  </si>
-  <si>
-    <t>0.1884,0.8889,0.0059,0.0002</t>
-  </si>
-  <si>
-    <t>0.6664,0.5942,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.9871,0.0008,0.0150,0.0002</t>
-  </si>
-  <si>
-    <t>0.9980,0.0002,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.8964,0.0030,0.1985,0.0011</t>
-  </si>
-  <si>
-    <t>0.9893,0.0030,0.0036,0.0001</t>
-  </si>
-  <si>
-    <t>0.9197,0.0182,0.0731,0.0005</t>
-  </si>
-  <si>
-    <t>0.9836,0.0008,0.0187,0.0004</t>
-  </si>
-  <si>
-    <t>0.8504,0.0031,0.2649,0.0014</t>
-  </si>
-  <si>
-    <t>0.7161,0.4418,0.0050,0.0002</t>
-  </si>
-  <si>
-    <t>0.9715,0.0202,0.0059,0.0003</t>
-  </si>
-  <si>
-    <t>0.0289,0.0269,0.9772,0.0016</t>
-  </si>
-  <si>
-    <t>0.5148,0.6448,0.0051,0.0001</t>
-  </si>
-  <si>
-    <t>0.9418,0.0516,0.0046,0.0008</t>
-  </si>
-  <si>
-    <t>0.9370,0.0608,0.0062,0.0007</t>
-  </si>
-  <si>
-    <t>0.8413,0.2014,0.0065,0.0010</t>
-  </si>
-  <si>
-    <t>0.9921,0.0052,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.8933,0.0588,0.0205,0.0001</t>
-  </si>
-  <si>
-    <t>0.9897,0.0003,0.0162,0.0002</t>
-  </si>
-  <si>
-    <t>0.9321,0.0025,0.1374,0.0004</t>
-  </si>
-  <si>
-    <t>0.9941,0.0003,0.0045,0.0002</t>
-  </si>
-  <si>
-    <t>0.9761,0.0030,0.0226,0.0003</t>
-  </si>
-  <si>
-    <t>0.4393,0.4384,0.0240,0.0001</t>
-  </si>
-  <si>
-    <t>0.9295,0.0024,0.1172,0.0002</t>
-  </si>
-  <si>
-    <t>0.8575,0.1411,0.0168,0.0012</t>
-  </si>
-  <si>
-    <t>0.9591,0.0279,0.0042,0.0001</t>
-  </si>
-  <si>
-    <t>0.9276,0.0583,0.0066,0.0001</t>
-  </si>
-  <si>
-    <t>0.9594,0.0430,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.0184,0.1980,0.9601,0.0013</t>
-  </si>
-  <si>
-    <t>0.1710,0.0249,0.9018,0.0004</t>
-  </si>
-  <si>
-    <t>0.9671,0.0033,0.0452,0.0004</t>
-  </si>
-  <si>
-    <t>0.9219,0.0080,0.0910,0.0002</t>
-  </si>
-  <si>
-    <t>0.0835,0.0193,0.9083,0.0005</t>
-  </si>
-  <si>
-    <t>0.4871,0.0142,0.4480,0.0001</t>
-  </si>
-  <si>
-    <t>0.9505,0.0409,0.0023,0.0011</t>
-  </si>
-  <si>
-    <t>0.8015,0.2143,0.0082,0.0018</t>
-  </si>
-  <si>
-    <t>0.9686,0.0208,0.0008,0.0012</t>
-  </si>
-  <si>
-    <t>0.5237,0.4037,0.1289,0.0043</t>
-  </si>
-  <si>
-    <t>0.8931,0.0801,0.0024,0.0020</t>
-  </si>
-  <si>
-    <t>0.8963,0.1914,0.0024,0.0002</t>
-  </si>
-  <si>
-    <t>0.9470,0.0518,0.0019,0.0008</t>
-  </si>
-  <si>
-    <t>0.3197,0.2255,0.3290,0.0003</t>
-  </si>
-  <si>
-    <t>0.7883,0.0014,0.4508,0.0002</t>
-  </si>
-  <si>
-    <t>0.8710,0.0027,0.2450,0.0006</t>
-  </si>
-  <si>
-    <t>0.5345,0.2889,0.0967,0.0004</t>
-  </si>
-  <si>
-    <t>0.8290,0.0031,0.3330,0.0005</t>
-  </si>
-  <si>
-    <t>0.9209,0.1232,0.0026,0.0000</t>
-  </si>
-  <si>
-    <t>0.5326,0.6883,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.9664,0.0249,0.0042,0.0006</t>
-  </si>
-  <si>
-    <t>0.9465,0.0192,0.0295,0.0008</t>
-  </si>
-  <si>
-    <t>0.0606,0.1734,0.8245,0.0023</t>
-  </si>
-  <si>
-    <t>0.5864,0.0111,0.5475,0.0002</t>
-  </si>
-  <si>
-    <t>0.7627,0.0489,0.1922,0.0008</t>
-  </si>
-  <si>
-    <t>0.1626,0.8336,0.0070,0.0000</t>
-  </si>
-  <si>
-    <t>0.4217,0.0548,0.5487,0.0013</t>
-  </si>
-  <si>
-    <t>0.9847,0.0038,0.0027,0.0009</t>
-  </si>
-  <si>
-    <t>0.9510,0.0180,0.0043,0.0052</t>
-  </si>
-  <si>
-    <t>0.9699,0.0057,0.0073,0.0027</t>
-  </si>
-  <si>
-    <t>0.9674,0.0115,0.0057,0.0030</t>
-  </si>
-  <si>
-    <t>0.9642,0.0042,0.0040,0.0141</t>
-  </si>
-  <si>
-    <t>0.9852,0.0064,0.0017,0.0005</t>
-  </si>
-  <si>
-    <t>0.4734,0.3967,0.0624,0.0001</t>
-  </si>
-  <si>
-    <t>0.0855,0.2322,0.7073,0.0010</t>
-  </si>
-  <si>
-    <t>0.7363,0.0419,0.1460,0.0002</t>
-  </si>
-  <si>
-    <t>0.9299,0.0044,0.1247,0.0002</t>
-  </si>
-  <si>
-    <t>0.5144,0.1128,0.3137,0.0006</t>
-  </si>
-  <si>
-    <t>0.9145,0.0384,0.0155,0.0001</t>
-  </si>
-  <si>
-    <t>0.7574,0.3548,0.0125,0.0009</t>
-  </si>
-  <si>
-    <t>0.9437,0.0854,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.9436,0.0559,0.0012,0.0009</t>
-  </si>
-  <si>
-    <t>0.9718,0.0265,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9882,0.0068,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9823,0.0136,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.8246,0.2652,0.0057,0.0007</t>
-  </si>
-  <si>
-    <t>0.9725,0.0180,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9435,0.0605,0.0009,0.0007</t>
-  </si>
-  <si>
-    <t>0.9617,0.0287,0.0015,0.0008</t>
-  </si>
-  <si>
-    <t>0.9162,0.0825,0.0013,0.0008</t>
-  </si>
-  <si>
-    <t>0.8599,0.1465,0.0068,0.0021</t>
-  </si>
-  <si>
-    <t>0.7208,0.3059,0.0070,0.0019</t>
-  </si>
-  <si>
-    <t>0.9651,0.0379,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.9172,0.1044,0.0019,0.0005</t>
-  </si>
-  <si>
-    <t>0.8755,0.1754,0.0028,0.0007</t>
-  </si>
-  <si>
-    <t>0.0435,0.0822,0.9588,0.0016</t>
-  </si>
-  <si>
-    <t>0.9872,0.0021,0.0108,0.0002</t>
-  </si>
-  <si>
-    <t>0.9534,0.0064,0.0469,0.0012</t>
-  </si>
-  <si>
-    <t>0.9762,0.0021,0.0259,0.0001</t>
-  </si>
-  <si>
-    <t>0.5841,0.6234,0.0036,0.0002</t>
-  </si>
-  <si>
-    <t>0.4784,0.6660,0.0044,0.0006</t>
-  </si>
-  <si>
-    <t>0.6647,0.4704,0.0033,0.0005</t>
-  </si>
-  <si>
-    <t>0.9578,0.0407,0.0024,0.0006</t>
-  </si>
-  <si>
-    <t>0.2730,0.8517,0.0099,0.0003</t>
-  </si>
-  <si>
-    <t>0.1028,0.9482,0.0028,0.0002</t>
-  </si>
-  <si>
-    <t>0.8699,0.1974,0.0041,0.0004</t>
-  </si>
-  <si>
-    <t>0.8643,0.0583,0.0415,0.0017</t>
-  </si>
-  <si>
-    <t>0.8699,0.0206,0.1493,0.0045</t>
-  </si>
-  <si>
-    <t>0.9878,0.0032,0.0037,0.0003</t>
-  </si>
-  <si>
-    <t>0.9808,0.0083,0.0047,0.0002</t>
-  </si>
-  <si>
-    <t>0.9761,0.0076,0.0061,0.0008</t>
-  </si>
-  <si>
-    <t>0.8587,0.2420,0.0016,0.0000</t>
-  </si>
-  <si>
-    <t>0.9706,0.0229,0.0039,0.0000</t>
-  </si>
-  <si>
-    <t>0.6493,0.3871,0.0291,0.0011</t>
-  </si>
-  <si>
-    <t>0.4780,0.3504,0.0364,0.0002</t>
-  </si>
-  <si>
-    <t>0.9715,0.0333,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.9188,0.1122,0.0015,0.0002</t>
-  </si>
-  <si>
-    <t>0.8953,0.1243,0.0049,0.0008</t>
-  </si>
-  <si>
-    <t>0.8968,0.1102,0.0060,0.0020</t>
-  </si>
-  <si>
-    <t>0.8272,0.2763,0.0063,0.0007</t>
-  </si>
-  <si>
-    <t>0.9600,0.0362,0.0016,0.0006</t>
-  </si>
-  <si>
-    <t>0.9408,0.0750,0.0016,0.0004</t>
-  </si>
-  <si>
-    <t>0.9097,0.1247,0.0041,0.0016</t>
-  </si>
-  <si>
-    <t>0.9229,0.0754,0.0075,0.0013</t>
-  </si>
-  <si>
-    <t>0.8611,0.1652,0.0077,0.0012</t>
-  </si>
-  <si>
-    <t>0.7928,0.2928,0.0096,0.0018</t>
-  </si>
-  <si>
-    <t>0.9221,0.0034,0.1646,0.0004</t>
-  </si>
-  <si>
-    <t>0.9436,0.0108,0.0414,0.0003</t>
-  </si>
-  <si>
-    <t>0.8441,0.0084,0.2136,0.0003</t>
-  </si>
-  <si>
-    <t>0.9907,0.0005,0.0138,0.0001</t>
-  </si>
-  <si>
-    <t>0.9889,0.0030,0.0055,0.0001</t>
-  </si>
-  <si>
-    <t>0.9672,0.0141,0.0086,0.0005</t>
-  </si>
-  <si>
-    <t>0.8989,0.0377,0.0514,0.0013</t>
-  </si>
-  <si>
-    <t>0.9899,0.0023,0.0030,0.0002</t>
-  </si>
-  <si>
-    <t>0.9867,0.0041,0.0016,0.0007</t>
-  </si>
-  <si>
-    <t>0.9731,0.0031,0.0026,0.0103</t>
-  </si>
-  <si>
-    <t>0.9665,0.0040,0.0103,0.0057</t>
-  </si>
-  <si>
-    <t>0.9557,0.0088,0.0032,0.0057</t>
-  </si>
-  <si>
-    <t>0.6679,0.0722,0.1986,0.0005</t>
-  </si>
-  <si>
-    <t>0.9499,0.0297,0.0041,0.0030</t>
-  </si>
-  <si>
-    <t>0.9428,0.0579,0.0025,0.0009</t>
-  </si>
-  <si>
-    <t>0.8335,0.2519,0.0027,0.0007</t>
-  </si>
-  <si>
-    <t>0.7313,0.3973,0.0097,0.0008</t>
-  </si>
-  <si>
-    <t>0.8129,0.2721,0.0045,0.0007</t>
-  </si>
-  <si>
-    <t>0.9190,0.0724,0.0066,0.0022</t>
-  </si>
-  <si>
-    <t>0.8351,0.1578,0.0083,0.0024</t>
-  </si>
-  <si>
-    <t>0.4276,0.0898,0.6558,0.0250</t>
-  </si>
-  <si>
-    <t>0.9650,0.0157,0.0021,0.0014</t>
-  </si>
-  <si>
-    <t>0.9613,0.0204,0.0008,0.0011</t>
-  </si>
-  <si>
-    <t>0.8851,0.1493,0.0096,0.0006</t>
-  </si>
-  <si>
-    <t>0.9679,0.0256,0.0027,0.0005</t>
-  </si>
-  <si>
-    <t>0.9817,0.0122,0.0018,0.0002</t>
-  </si>
-  <si>
-    <t>0.8972,0.1089,0.0076,0.0004</t>
-  </si>
-  <si>
-    <t>0.9842,0.0088,0.0017,0.0003</t>
-  </si>
-  <si>
-    <t>0.9896,0.0096,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.7860,0.2507,0.0055,0.0010</t>
-  </si>
-  <si>
-    <t>0.9445,0.0696,0.0009,0.0004</t>
-  </si>
-  <si>
-    <t>0.8946,0.1311,0.0021,0.0008</t>
-  </si>
-  <si>
-    <t>0.8762,0.1337,0.0017,0.0008</t>
-  </si>
-  <si>
-    <t>0.9207,0.0642,0.0038,0.0021</t>
-  </si>
-  <si>
-    <t>0.9424,0.0645,0.0016,0.0005</t>
-  </si>
-  <si>
-    <t>0.9526,0.0278,0.0015,0.0016</t>
-  </si>
-  <si>
-    <t>0.9670,0.0360,0.0014,0.0003</t>
-  </si>
-  <si>
-    <t>0.9034,0.1338,0.0017,0.0005</t>
-  </si>
-  <si>
-    <t>0.8753,0.1985,0.0024,0.0002</t>
-  </si>
-  <si>
-    <t>0.9024,0.1457,0.0028,0.0003</t>
-  </si>
-  <si>
-    <t>0.6113,0.4351,0.0452,0.0022</t>
-  </si>
-  <si>
-    <t>0.9713,0.0282,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.9395,0.0368,0.0059,0.0023</t>
-  </si>
-  <si>
-    <t>0.8834,0.1446,0.0038,0.0006</t>
-  </si>
-  <si>
-    <t>0.5051,0.6537,0.0034,0.0005</t>
-  </si>
-  <si>
-    <t>0.1317,0.0863,0.8727,0.0011</t>
-  </si>
-  <si>
-    <t>0.8312,0.2247,0.0049,0.0009</t>
-  </si>
-  <si>
-    <t>0.7969,0.0041,0.2805,0.0001</t>
-  </si>
-  <si>
-    <t>0.8217,0.0016,0.3780,0.0004</t>
-  </si>
-  <si>
-    <t>0.9229,0.0141,0.0769,0.0016</t>
-  </si>
-  <si>
-    <t>0.1841,0.0969,0.8570,0.0006</t>
-  </si>
-  <si>
-    <t>0.9326,0.0054,0.0805,0.0005</t>
-  </si>
-  <si>
-    <t>0.4399,0.0199,0.7103,0.0028</t>
-  </si>
-  <si>
-    <t>0.9848,0.0020,0.0152,0.0002</t>
-  </si>
-  <si>
-    <t>0.9481,0.0081,0.0433,0.0008</t>
-  </si>
-  <si>
-    <t>0.9446,0.0299,0.0170,0.0005</t>
-  </si>
-  <si>
-    <t>0.9550,0.0053,0.0414,0.0014</t>
-  </si>
-  <si>
-    <t>0.9089,0.1093,0.0047,0.0002</t>
-  </si>
-  <si>
-    <t>0.8369,0.1132,0.0245,0.0003</t>
-  </si>
-  <si>
-    <t>0.9879,0.0065,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.9631,0.0198,0.0052,0.0008</t>
-  </si>
-  <si>
-    <t>0.9688,0.0078,0.0225,0.0004</t>
-  </si>
-  <si>
-    <t>0.8373,0.2569,0.0049,0.0004</t>
-  </si>
-  <si>
-    <t>0.9447,0.0560,0.0016,0.0008</t>
-  </si>
-  <si>
-    <t>0.7587,0.2359,0.0057,0.0039</t>
-  </si>
-  <si>
-    <t>0.9180,0.1163,0.0012,0.0004</t>
-  </si>
-  <si>
-    <t>0.9837,0.0166,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9735,0.0148,0.0057,0.0002</t>
-  </si>
-  <si>
-    <t>0.9931,0.0026,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.9968,0.0003,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.9897,0.0014,0.0077,0.0001</t>
-  </si>
-  <si>
-    <t>0.9818,0.0043,0.0084,0.0006</t>
-  </si>
-  <si>
-    <t>0.7756,0.0557,0.1256,0.0005</t>
-  </si>
-  <si>
-    <t>0.9855,0.0010,0.0206,0.0002</t>
-  </si>
-  <si>
-    <t>0.9961,0.0004,0.0034,0.0000</t>
-  </si>
-  <si>
-    <t>0.9719,0.0019,0.0416,0.0004</t>
-  </si>
-  <si>
-    <t>0.7793,0.1029,0.0547,0.0005</t>
-  </si>
-  <si>
-    <t>0.9748,0.0184,0.0006,0.0005</t>
-  </si>
-  <si>
-    <t>0.9554,0.0376,0.0022,0.0010</t>
-  </si>
-  <si>
-    <t>0.9479,0.0545,0.0016,0.0006</t>
-  </si>
-  <si>
-    <t>0.9820,0.0140,0.0008,0.0005</t>
-  </si>
-  <si>
-    <t>0.9585,0.0423,0.0013,0.0004</t>
-  </si>
-  <si>
-    <t>0.9288,0.1077,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.8676,0.1061,0.0032,0.0032</t>
-  </si>
-  <si>
-    <t>0.9526,0.0384,0.0013,0.0012</t>
-  </si>
-  <si>
-    <t>0.9204,0.0559,0.0169,0.0004</t>
-  </si>
-  <si>
-    <t>0.8531,0.1225,0.0319,0.0013</t>
-  </si>
-  <si>
-    <t>0.9628,0.0226,0.0035,0.0018</t>
-  </si>
-  <si>
-    <t>0.3700,0.0133,0.7609,0.0010</t>
-  </si>
-  <si>
-    <t>0.2615,0.0132,0.8077,0.0015</t>
-  </si>
-  <si>
-    <t>0.8121,0.0247,0.2385,0.0012</t>
-  </si>
-  <si>
-    <t>0.3515,0.0087,0.8252,0.0007</t>
-  </si>
-  <si>
-    <t>0.9298,0.0095,0.0713,0.0003</t>
-  </si>
-  <si>
-    <t>0.0269,0.0109,0.9710,0.0021</t>
-  </si>
-  <si>
-    <t>0.7666,0.0044,0.4295,0.0004</t>
-  </si>
-  <si>
-    <t>0.9101,0.0676,0.0197,0.0009</t>
-  </si>
-  <si>
-    <t>0.9895,0.0016,0.0056,0.0002</t>
-  </si>
-  <si>
-    <t>0.9280,0.0293,0.0355,0.0014</t>
-  </si>
-  <si>
-    <t>0.9659,0.0270,0.0046,0.0002</t>
-  </si>
-  <si>
-    <t>0.9521,0.0473,0.0006,0.0005</t>
-  </si>
-  <si>
-    <t>0.9749,0.0277,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9419,0.0719,0.0030,0.0005</t>
-  </si>
-  <si>
-    <t>0.9883,0.0094,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9359,0.0668,0.0053,0.0011</t>
-  </si>
-  <si>
-    <t>0.8522,0.1931,0.0050,0.0021</t>
-  </si>
-  <si>
-    <t>0.8008,0.2635,0.0024,0.0008</t>
-  </si>
-  <si>
-    <t>0.8808,0.1738,0.0030,0.0007</t>
-  </si>
-  <si>
-    <t>0.9740,0.0070,0.0134,0.0002</t>
-  </si>
-  <si>
-    <t>0.6099,0.0063,0.5406,0.0023</t>
-  </si>
-  <si>
-    <t>0.1859,0.0202,0.7980,0.0017</t>
-  </si>
-  <si>
-    <t>0.9947,0.0007,0.0030,0.0001</t>
-  </si>
-  <si>
-    <t>0.9336,0.0030,0.1218,0.0004</t>
-  </si>
-  <si>
-    <t>0.9841,0.0030,0.0086,0.0004</t>
-  </si>
-  <si>
-    <t>0.9757,0.0051,0.0184,0.0006</t>
-  </si>
-  <si>
-    <t>0.9967,0.0001,0.0034,0.0001</t>
-  </si>
-  <si>
-    <t>0.9556,0.0204,0.0042,0.0017</t>
-  </si>
-  <si>
-    <t>0.9798,0.0018,0.0089,0.0015</t>
-  </si>
-  <si>
-    <t>0.9808,0.0037,0.0020,0.0028</t>
-  </si>
-  <si>
-    <t>0.9773,0.0026,0.0036,0.0041</t>
-  </si>
-  <si>
-    <t>0.9459,0.0092,0.0052,0.0172</t>
-  </si>
-  <si>
-    <t>0.9644,0.0159,0.0047,0.0005</t>
+    <t>0.9119,0.0820,0.0099,0.0006</t>
+  </si>
+  <si>
+    <t>0.9553,0.0132,0.0051,0.0046</t>
+  </si>
+  <si>
+    <t>0.9193,0.0456,0.0029,0.0022</t>
+  </si>
+  <si>
+    <t>0.9639,0.0151,0.0026,0.0025</t>
+  </si>
+  <si>
+    <t>0.8932,0.1334,0.0035,0.0013</t>
+  </si>
+  <si>
+    <t>0.8202,0.1689,0.0093,0.0035</t>
+  </si>
+  <si>
+    <t>0.8959,0.1441,0.0027,0.0006</t>
+  </si>
+  <si>
+    <t>0.9768,0.0188,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.9865,0.0057,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.7756,0.3352,0.0036,0.0005</t>
+  </si>
+  <si>
+    <t>0.9349,0.0830,0.0011,0.0008</t>
+  </si>
+  <si>
+    <t>0.9358,0.0727,0.0017,0.0008</t>
+  </si>
+  <si>
+    <t>0.9913,0.0015,0.0046,0.0002</t>
+  </si>
+  <si>
+    <t>0.9701,0.0117,0.0110,0.0003</t>
+  </si>
+  <si>
+    <t>0.9240,0.0151,0.0703,0.0006</t>
+  </si>
+  <si>
+    <t>0.9578,0.0145,0.0152,0.0004</t>
+  </si>
+  <si>
+    <t>0.9796,0.0100,0.0022,0.0004</t>
+  </si>
+  <si>
+    <t>0.9249,0.1279,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.8004,0.2844,0.0059,0.0003</t>
+  </si>
+  <si>
+    <t>0.9525,0.0374,0.0041,0.0010</t>
+  </si>
+  <si>
+    <t>0.3997,0.7710,0.0064,0.0004</t>
+  </si>
+  <si>
+    <t>0.3424,0.7910,0.0090,0.0003</t>
+  </si>
+  <si>
+    <t>0.9675,0.0055,0.0236,0.0003</t>
+  </si>
+  <si>
+    <t>0.9829,0.0024,0.0158,0.0002</t>
+  </si>
+  <si>
+    <t>0.8292,0.0020,0.3668,0.0004</t>
+  </si>
+  <si>
+    <t>0.9890,0.0020,0.0074,0.0002</t>
+  </si>
+  <si>
+    <t>0.9858,0.0016,0.0173,0.0001</t>
+  </si>
+  <si>
+    <t>0.9576,0.0042,0.0533,0.0007</t>
+  </si>
+  <si>
+    <t>0.6847,0.0022,0.5697,0.0005</t>
+  </si>
+  <si>
+    <t>0.9705,0.0281,0.0015,0.0003</t>
+  </si>
+  <si>
+    <t>0.9659,0.0246,0.0044,0.0003</t>
+  </si>
+  <si>
+    <t>0.0569,0.1392,0.8939,0.0021</t>
+  </si>
+  <si>
+    <t>0.3339,0.7401,0.0051,0.0000</t>
+  </si>
+  <si>
+    <t>0.7733,0.2120,0.0164,0.0034</t>
+  </si>
+  <si>
+    <t>0.9621,0.0273,0.0026,0.0006</t>
+  </si>
+  <si>
+    <t>0.9645,0.0335,0.0015,0.0003</t>
+  </si>
+  <si>
+    <t>0.9868,0.0114,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.9542,0.0021,0.0683,0.0003</t>
+  </si>
+  <si>
+    <t>0.8304,0.0011,0.3977,0.0002</t>
+  </si>
+  <si>
+    <t>0.9397,0.0062,0.0758,0.0019</t>
+  </si>
+  <si>
+    <t>0.9951,0.0002,0.0017,0.0004</t>
+  </si>
+  <si>
+    <t>0.9873,0.0007,0.0186,0.0000</t>
+  </si>
+  <si>
+    <t>0.3308,0.1525,0.1353,0.0002</t>
+  </si>
+  <si>
+    <t>0.9749,0.0017,0.0337,0.0001</t>
+  </si>
+  <si>
+    <t>0.7829,0.2791,0.0117,0.0010</t>
+  </si>
+  <si>
+    <t>0.9703,0.0441,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.9542,0.0332,0.0060,0.0001</t>
+  </si>
+  <si>
+    <t>0.9288,0.0876,0.0024,0.0001</t>
+  </si>
+  <si>
+    <t>0.1124,0.1204,0.7988,0.0017</t>
+  </si>
+  <si>
+    <t>0.0332,0.0098,0.9695,0.0006</t>
+  </si>
+  <si>
+    <t>0.9851,0.0032,0.0128,0.0001</t>
+  </si>
+  <si>
+    <t>0.6468,0.0117,0.5416,0.0024</t>
+  </si>
+  <si>
+    <t>0.0211,0.0041,0.9850,0.0002</t>
+  </si>
+  <si>
+    <t>0.5436,0.0090,0.6422,0.0009</t>
+  </si>
+  <si>
+    <t>0.9318,0.0499,0.0012,0.0012</t>
+  </si>
+  <si>
+    <t>0.9459,0.0571,0.0019,0.0005</t>
+  </si>
+  <si>
+    <t>0.9720,0.0200,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.3770,0.1659,0.6369,0.0067</t>
+  </si>
+  <si>
+    <t>0.9698,0.0242,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.9487,0.0507,0.0013,0.0007</t>
+  </si>
+  <si>
+    <t>0.8589,0.1917,0.0071,0.0008</t>
+  </si>
+  <si>
+    <t>0.1586,0.0175,0.9061,0.0002</t>
+  </si>
+  <si>
+    <t>0.0728,0.0071,0.9662,0.0005</t>
+  </si>
+  <si>
+    <t>0.5899,0.0061,0.5795,0.0018</t>
+  </si>
+  <si>
+    <t>0.3727,0.4544,0.0570,0.0002</t>
+  </si>
+  <si>
+    <t>0.4772,0.0022,0.7802,0.0002</t>
+  </si>
+  <si>
+    <t>0.9097,0.1356,0.0018,0.0000</t>
+  </si>
+  <si>
+    <t>0.1586,0.9279,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9656,0.0224,0.0053,0.0006</t>
+  </si>
+  <si>
+    <t>0.9479,0.0412,0.0069,0.0003</t>
+  </si>
+  <si>
+    <t>0.0893,0.4952,0.7937,0.0054</t>
+  </si>
+  <si>
+    <t>0.8971,0.0156,0.1124,0.0003</t>
+  </si>
+  <si>
+    <t>0.9220,0.0058,0.1304,0.0002</t>
+  </si>
+  <si>
+    <t>0.6154,0.3708,0.0098,0.0001</t>
+  </si>
+  <si>
+    <t>0.2956,0.0226,0.6869,0.0012</t>
+  </si>
+  <si>
+    <t>0.9480,0.0180,0.0055,0.0031</t>
+  </si>
+  <si>
+    <t>0.9236,0.0377,0.0023,0.0066</t>
+  </si>
+  <si>
+    <t>0.8925,0.0202,0.0300,0.0172</t>
+  </si>
+  <si>
+    <t>0.9789,0.0060,0.0070,0.0011</t>
+  </si>
+  <si>
+    <t>0.9675,0.0102,0.0029,0.0053</t>
+  </si>
+  <si>
+    <t>0.9948,0.0011,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9536,0.0115,0.0267,0.0003</t>
+  </si>
+  <si>
+    <t>0.8482,0.0362,0.0872,0.0010</t>
+  </si>
+  <si>
+    <t>0.5958,0.0143,0.5401,0.0021</t>
+  </si>
+  <si>
+    <t>0.9609,0.0030,0.0641,0.0004</t>
+  </si>
+  <si>
+    <t>0.5455,0.1563,0.1216,0.0001</t>
+  </si>
+  <si>
+    <t>0.9548,0.0101,0.0380,0.0001</t>
+  </si>
+  <si>
+    <t>0.9709,0.0235,0.0022,0.0006</t>
+  </si>
+  <si>
+    <t>0.9738,0.0241,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.8140,0.2533,0.0049,0.0011</t>
+  </si>
+  <si>
+    <t>0.9697,0.0226,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.8918,0.1502,0.0033,0.0009</t>
+  </si>
+  <si>
+    <t>0.9748,0.0188,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.9268,0.0729,0.0022,0.0007</t>
+  </si>
+  <si>
+    <t>0.8571,0.2124,0.0024,0.0007</t>
+  </si>
+  <si>
+    <t>0.9582,0.0428,0.0008,0.0006</t>
+  </si>
+  <si>
+    <t>0.9474,0.0466,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.9781,0.0176,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9897,0.0037,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9473,0.0526,0.0013,0.0006</t>
+  </si>
+  <si>
+    <t>0.9635,0.0245,0.0010,0.0009</t>
+  </si>
+  <si>
+    <t>0.9543,0.0282,0.0015,0.0019</t>
+  </si>
+  <si>
+    <t>0.9668,0.0211,0.0011,0.0012</t>
+  </si>
+  <si>
+    <t>0.7804,0.0274,0.3443,0.0011</t>
+  </si>
+  <si>
+    <t>0.2687,0.0148,0.8266,0.0024</t>
+  </si>
+  <si>
+    <t>0.9897,0.0017,0.0029,0.0003</t>
+  </si>
+  <si>
+    <t>0.9211,0.0058,0.1329,0.0018</t>
+  </si>
+  <si>
+    <t>0.3930,0.7594,0.0131,0.0005</t>
+  </si>
+  <si>
+    <t>0.9275,0.1107,0.0017,0.0002</t>
+  </si>
+  <si>
+    <t>0.6470,0.4656,0.0113,0.0005</t>
+  </si>
+  <si>
+    <t>0.8961,0.1553,0.0029,0.0004</t>
+  </si>
+  <si>
+    <t>0.7280,0.4083,0.0086,0.0005</t>
+  </si>
+  <si>
+    <t>0.2906,0.8393,0.0036,0.0004</t>
+  </si>
+  <si>
+    <t>0.5818,0.5802,0.0120,0.0010</t>
+  </si>
+  <si>
+    <t>0.8758,0.1042,0.0189,0.0011</t>
+  </si>
+  <si>
+    <t>0.9615,0.0144,0.0157,0.0008</t>
+  </si>
+  <si>
+    <t>0.9818,0.0088,0.0030,0.0002</t>
+  </si>
+  <si>
+    <t>0.9716,0.0147,0.0048,0.0003</t>
+  </si>
+  <si>
+    <t>0.9719,0.0114,0.0111,0.0006</t>
+  </si>
+  <si>
+    <t>0.9227,0.1275,0.0024,0.0001</t>
+  </si>
+  <si>
+    <t>0.9365,0.0714,0.0033,0.0000</t>
+  </si>
+  <si>
+    <t>0.5741,0.5399,0.0097,0.0006</t>
+  </si>
+  <si>
+    <t>0.5251,0.3184,0.0307,0.0001</t>
+  </si>
+  <si>
+    <t>0.8925,0.1688,0.0025,0.0001</t>
+  </si>
+  <si>
+    <t>0.8624,0.2117,0.0032,0.0004</t>
+  </si>
+  <si>
+    <t>0.7426,0.3353,0.0077,0.0010</t>
+  </si>
+  <si>
+    <t>0.9894,0.0082,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9070,0.1457,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.9529,0.0599,0.0014,0.0005</t>
+  </si>
+  <si>
+    <t>0.9422,0.0674,0.0016,0.0003</t>
+  </si>
+  <si>
+    <t>0.9708,0.0144,0.0008,0.0015</t>
+  </si>
+  <si>
+    <t>0.9629,0.0340,0.0040,0.0009</t>
+  </si>
+  <si>
+    <t>0.9092,0.0566,0.0040,0.0025</t>
+  </si>
+  <si>
+    <t>0.7184,0.3946,0.0076,0.0014</t>
+  </si>
+  <si>
+    <t>0.4573,0.0191,0.6872,0.0010</t>
+  </si>
+  <si>
+    <t>0.3010,0.0759,0.7667,0.0007</t>
+  </si>
+  <si>
+    <t>0.7730,0.0016,0.4303,0.0004</t>
+  </si>
+  <si>
+    <t>0.9916,0.0012,0.0103,0.0001</t>
+  </si>
+  <si>
+    <t>0.9501,0.0238,0.0218,0.0004</t>
+  </si>
+  <si>
+    <t>0.9742,0.0151,0.0051,0.0003</t>
+  </si>
+  <si>
+    <t>0.9706,0.0126,0.0080,0.0003</t>
+  </si>
+  <si>
+    <t>0.9827,0.0078,0.0027,0.0001</t>
+  </si>
+  <si>
+    <t>0.9869,0.0021,0.0020,0.0015</t>
+  </si>
+  <si>
+    <t>0.9552,0.0133,0.0067,0.0080</t>
+  </si>
+  <si>
+    <t>0.9691,0.0046,0.0053,0.0057</t>
+  </si>
+  <si>
+    <t>0.9774,0.0076,0.0022,0.0013</t>
+  </si>
+  <si>
+    <t>0.8236,0.0453,0.0463,0.0003</t>
+  </si>
+  <si>
+    <t>0.9375,0.0570,0.0028,0.0013</t>
+  </si>
+  <si>
+    <t>0.8334,0.2548,0.0059,0.0007</t>
+  </si>
+  <si>
+    <t>0.8920,0.1315,0.0019,0.0004</t>
+  </si>
+  <si>
+    <t>0.6264,0.5517,0.0061,0.0005</t>
+  </si>
+  <si>
+    <t>0.9240,0.0764,0.0041,0.0008</t>
+  </si>
+  <si>
+    <t>0.9787,0.0111,0.0025,0.0007</t>
+  </si>
+  <si>
+    <t>0.8605,0.1385,0.0076,0.0025</t>
+  </si>
+  <si>
+    <t>0.2392,0.2142,0.7716,0.0090</t>
+  </si>
+  <si>
+    <t>0.9707,0.0128,0.0009,0.0012</t>
+  </si>
+  <si>
+    <t>0.9376,0.0493,0.0045,0.0017</t>
+  </si>
+  <si>
+    <t>0.9632,0.0343,0.0027,0.0004</t>
+  </si>
+  <si>
+    <t>0.9021,0.1154,0.0057,0.0003</t>
+  </si>
+  <si>
+    <t>0.9355,0.0797,0.0037,0.0002</t>
+  </si>
+  <si>
+    <t>0.8058,0.1949,0.0206,0.0010</t>
+  </si>
+  <si>
+    <t>0.9851,0.0091,0.0014,0.0002</t>
+  </si>
+  <si>
+    <t>0.9555,0.0584,0.0019,0.0002</t>
+  </si>
+  <si>
+    <t>0.9763,0.0135,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.9652,0.0356,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.9621,0.0285,0.0008,0.0008</t>
+  </si>
+  <si>
+    <t>0.9367,0.0519,0.0033,0.0016</t>
+  </si>
+  <si>
+    <t>0.9410,0.0579,0.0028,0.0011</t>
+  </si>
+  <si>
+    <t>0.9216,0.0819,0.0020,0.0006</t>
+  </si>
+  <si>
+    <t>0.9200,0.1000,0.0022,0.0006</t>
+  </si>
+  <si>
+    <t>0.9650,0.0336,0.0020,0.0005</t>
+  </si>
+  <si>
+    <t>0.8701,0.1538,0.0053,0.0009</t>
+  </si>
+  <si>
+    <t>0.7835,0.2735,0.0115,0.0006</t>
+  </si>
+  <si>
+    <t>0.5731,0.5683,0.0053,0.0003</t>
+  </si>
+  <si>
+    <t>0.4111,0.4123,0.1936,0.0020</t>
+  </si>
+  <si>
+    <t>0.9169,0.0997,0.0049,0.0008</t>
+  </si>
+  <si>
+    <t>0.7193,0.4033,0.0110,0.0009</t>
+  </si>
+  <si>
+    <t>0.9417,0.0647,0.0017,0.0004</t>
+  </si>
+  <si>
+    <t>0.8590,0.2520,0.0023,0.0003</t>
+  </si>
+  <si>
+    <t>0.0226,0.3220,0.9229,0.0011</t>
+  </si>
+  <si>
+    <t>0.9401,0.0599,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.7540,0.0017,0.4460,0.0007</t>
+  </si>
+  <si>
+    <t>0.9210,0.0056,0.1290,0.0007</t>
+  </si>
+  <si>
+    <t>0.9329,0.0187,0.0423,0.0016</t>
+  </si>
+  <si>
+    <t>0.2457,0.0269,0.8153,0.0005</t>
+  </si>
+  <si>
+    <t>0.8130,0.0078,0.2969,0.0011</t>
+  </si>
+  <si>
+    <t>0.6120,0.0109,0.5813,0.0011</t>
+  </si>
+  <si>
+    <t>0.7542,0.0066,0.4025,0.0014</t>
+  </si>
+  <si>
+    <t>0.9801,0.0053,0.0054,0.0002</t>
+  </si>
+  <si>
+    <t>0.9778,0.0108,0.0047,0.0002</t>
+  </si>
+  <si>
+    <t>0.9157,0.0345,0.0275,0.0021</t>
+  </si>
+  <si>
+    <t>0.9813,0.0075,0.0058,0.0002</t>
+  </si>
+  <si>
+    <t>0.7658,0.2120,0.0246,0.0007</t>
+  </si>
+  <si>
+    <t>0.8876,0.0834,0.0236,0.0006</t>
+  </si>
+  <si>
+    <t>0.9804,0.0047,0.0100,0.0005</t>
+  </si>
+  <si>
+    <t>0.9931,0.0028,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.7949,0.3428,0.0041,0.0003</t>
+  </si>
+  <si>
+    <t>0.8730,0.1800,0.0041,0.0006</t>
+  </si>
+  <si>
+    <t>0.8815,0.1707,0.0053,0.0005</t>
+  </si>
+  <si>
+    <t>0.7433,0.4422,0.0036,0.0003</t>
+  </si>
+  <si>
+    <t>0.9594,0.0333,0.0007,0.0006</t>
+  </si>
+  <si>
+    <t>0.9086,0.0720,0.0113,0.0007</t>
+  </si>
+  <si>
+    <t>0.9910,0.0030,0.0019,0.0001</t>
+  </si>
+  <si>
+    <t>0.9743,0.0054,0.0137,0.0007</t>
+  </si>
+  <si>
+    <t>0.9863,0.0041,0.0035,0.0002</t>
+  </si>
+  <si>
+    <t>0.9601,0.0151,0.0148,0.0008</t>
+  </si>
+  <si>
+    <t>0.9295,0.0245,0.0380,0.0011</t>
+  </si>
+  <si>
+    <t>0.9714,0.0029,0.0318,0.0004</t>
+  </si>
+  <si>
+    <t>0.9851,0.0016,0.0161,0.0001</t>
+  </si>
+  <si>
+    <t>0.9388,0.0022,0.1362,0.0005</t>
+  </si>
+  <si>
+    <t>0.9884,0.0021,0.0060,0.0001</t>
+  </si>
+  <si>
+    <t>0.9884,0.0060,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9403,0.0707,0.0013,0.0004</t>
+  </si>
+  <si>
+    <t>0.9546,0.0428,0.0016,0.0009</t>
+  </si>
+  <si>
+    <t>0.7852,0.2793,0.0030,0.0010</t>
+  </si>
+  <si>
+    <t>0.9463,0.0368,0.0021,0.0014</t>
+  </si>
+  <si>
+    <t>0.6458,0.4581,0.0155,0.0026</t>
+  </si>
+  <si>
+    <t>0.9118,0.1254,0.0018,0.0007</t>
+  </si>
+  <si>
+    <t>0.7109,0.3336,0.0049,0.0015</t>
+  </si>
+  <si>
+    <t>0.8997,0.1061,0.0137,0.0005</t>
+  </si>
+  <si>
+    <t>0.8727,0.1354,0.0101,0.0006</t>
+  </si>
+  <si>
+    <t>0.7673,0.2912,0.0244,0.0011</t>
+  </si>
+  <si>
+    <t>0.7651,0.0026,0.3875,0.0013</t>
+  </si>
+  <si>
+    <t>0.0820,0.0650,0.8782,0.0015</t>
+  </si>
+  <si>
+    <t>0.6674,0.0546,0.2980,0.0022</t>
+  </si>
+  <si>
+    <t>0.0372,0.0115,0.9806,0.0005</t>
+  </si>
+  <si>
+    <t>0.9223,0.0059,0.1025,0.0004</t>
+  </si>
+  <si>
+    <t>0.1249,0.0135,0.8335,0.0026</t>
+  </si>
+  <si>
+    <t>0.7103,0.0383,0.3220,0.0030</t>
+  </si>
+  <si>
+    <t>0.9321,0.0342,0.0208,0.0006</t>
+  </si>
+  <si>
+    <t>0.9669,0.0099,0.0217,0.0006</t>
+  </si>
+  <si>
+    <t>0.9702,0.0049,0.0226,0.0008</t>
+  </si>
+  <si>
+    <t>0.9936,0.0028,0.0010,0.0000</t>
+  </si>
+  <si>
+    <t>0.9463,0.0580,0.0012,0.0004</t>
+  </si>
+  <si>
+    <t>0.8528,0.1516,0.0055,0.0017</t>
+  </si>
+  <si>
+    <t>0.8103,0.1936,0.0050,0.0015</t>
+  </si>
+  <si>
+    <t>0.9237,0.0688,0.0013,0.0010</t>
+  </si>
+  <si>
+    <t>0.9215,0.0766,0.0038,0.0019</t>
+  </si>
+  <si>
+    <t>0.9623,0.0349,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.9687,0.0181,0.0006,0.0008</t>
+  </si>
+  <si>
+    <t>0.7903,0.3401,0.0039,0.0005</t>
+  </si>
+  <si>
+    <t>0.8174,0.0295,0.1919,0.0011</t>
+  </si>
+  <si>
+    <t>0.3637,0.0679,0.4016,0.0007</t>
+  </si>
+  <si>
+    <t>0.7413,0.0123,0.3661,0.0015</t>
+  </si>
+  <si>
+    <t>0.9675,0.0024,0.0406,0.0004</t>
+  </si>
+  <si>
+    <t>0.6968,0.0020,0.5090,0.0002</t>
+  </si>
+  <si>
+    <t>0.9852,0.0018,0.0096,0.0004</t>
+  </si>
+  <si>
+    <t>0.9711,0.0047,0.0255,0.0002</t>
+  </si>
+  <si>
+    <t>0.9936,0.0011,0.0034,0.0001</t>
+  </si>
+  <si>
+    <t>0.9765,0.0137,0.0009,0.0005</t>
+  </si>
+  <si>
+    <t>0.9866,0.0033,0.0044,0.0009</t>
+  </si>
+  <si>
+    <t>0.9735,0.0068,0.0033,0.0031</t>
+  </si>
+  <si>
+    <t>0.9819,0.0018,0.0032,0.0035</t>
+  </si>
+  <si>
+    <t>0.9701,0.0038,0.0031,0.0114</t>
+  </si>
+  <si>
+    <t>0.9692,0.0132,0.0063,0.0009</t>
   </si>
 </sst>
 </file>
@@ -2205,7 +2205,7 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D20" t="s">
         <v>282</v>
@@ -2345,7 +2345,7 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D30" t="s">
         <v>292</v>
@@ -2667,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
         <v>315</v>
@@ -2695,7 +2695,7 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
         <v>317</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2807,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D63" t="s">
         <v>325</v>
@@ -2821,7 +2821,7 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D64" t="s">
         <v>326</v>
@@ -2835,7 +2835,7 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
         <v>327</v>
@@ -2863,7 +2863,7 @@
         <v>261</v>
       </c>
       <c r="C67" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D67" t="s">
         <v>329</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2975,7 +2975,7 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D75" t="s">
         <v>337</v>
@@ -3101,7 +3101,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D84" t="s">
         <v>346</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3395,7 +3395,7 @@
         <v>261</v>
       </c>
       <c r="C105" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D105" t="s">
         <v>367</v>
@@ -3409,7 +3409,7 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
         <v>368</v>
@@ -3465,7 +3465,7 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D110" t="s">
         <v>372</v>
@@ -3507,7 +3507,7 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D113" t="s">
         <v>375</v>
@@ -3535,7 +3535,7 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
         <v>377</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -4053,7 +4053,7 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
         <v>414</v>
@@ -4375,7 +4375,7 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
         <v>437</v>
@@ -4445,7 +4445,7 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D180" t="s">
         <v>442</v>
@@ -5061,7 +5061,7 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D224" t="s">
         <v>486</v>
@@ -5341,7 +5341,7 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D244" t="s">
         <v>506</v>
@@ -5355,7 +5355,7 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D245" t="s">
         <v>507</v>
@@ -5383,7 +5383,7 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
         <v>509</v>

--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_60/per_file_predictions_epoch_60.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_60/per_file_predictions_epoch_60.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9119,0.0820,0.0099,0.0006</t>
-  </si>
-  <si>
-    <t>0.9553,0.0132,0.0051,0.0046</t>
-  </si>
-  <si>
-    <t>0.9193,0.0456,0.0029,0.0022</t>
-  </si>
-  <si>
-    <t>0.9639,0.0151,0.0026,0.0025</t>
-  </si>
-  <si>
-    <t>0.8932,0.1334,0.0035,0.0013</t>
-  </si>
-  <si>
-    <t>0.8202,0.1689,0.0093,0.0035</t>
-  </si>
-  <si>
-    <t>0.8959,0.1441,0.0027,0.0006</t>
-  </si>
-  <si>
-    <t>0.9768,0.0188,0.0008,0.0005</t>
-  </si>
-  <si>
-    <t>0.9865,0.0057,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.7756,0.3352,0.0036,0.0005</t>
-  </si>
-  <si>
-    <t>0.9349,0.0830,0.0011,0.0008</t>
-  </si>
-  <si>
-    <t>0.9358,0.0727,0.0017,0.0008</t>
-  </si>
-  <si>
-    <t>0.9913,0.0015,0.0046,0.0002</t>
-  </si>
-  <si>
-    <t>0.9701,0.0117,0.0110,0.0003</t>
-  </si>
-  <si>
-    <t>0.9240,0.0151,0.0703,0.0006</t>
-  </si>
-  <si>
-    <t>0.9578,0.0145,0.0152,0.0004</t>
-  </si>
-  <si>
-    <t>0.9796,0.0100,0.0022,0.0004</t>
-  </si>
-  <si>
-    <t>0.9249,0.1279,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.8004,0.2844,0.0059,0.0003</t>
-  </si>
-  <si>
-    <t>0.9525,0.0374,0.0041,0.0010</t>
-  </si>
-  <si>
-    <t>0.3997,0.7710,0.0064,0.0004</t>
-  </si>
-  <si>
-    <t>0.3424,0.7910,0.0090,0.0003</t>
-  </si>
-  <si>
-    <t>0.9675,0.0055,0.0236,0.0003</t>
-  </si>
-  <si>
-    <t>0.9829,0.0024,0.0158,0.0002</t>
-  </si>
-  <si>
-    <t>0.8292,0.0020,0.3668,0.0004</t>
-  </si>
-  <si>
-    <t>0.9890,0.0020,0.0074,0.0002</t>
-  </si>
-  <si>
-    <t>0.9858,0.0016,0.0173,0.0001</t>
-  </si>
-  <si>
-    <t>0.9576,0.0042,0.0533,0.0007</t>
-  </si>
-  <si>
-    <t>0.6847,0.0022,0.5697,0.0005</t>
-  </si>
-  <si>
-    <t>0.9705,0.0281,0.0015,0.0003</t>
-  </si>
-  <si>
-    <t>0.9659,0.0246,0.0044,0.0003</t>
-  </si>
-  <si>
-    <t>0.0569,0.1392,0.8939,0.0021</t>
-  </si>
-  <si>
-    <t>0.3339,0.7401,0.0051,0.0000</t>
-  </si>
-  <si>
-    <t>0.7733,0.2120,0.0164,0.0034</t>
-  </si>
-  <si>
-    <t>0.9621,0.0273,0.0026,0.0006</t>
-  </si>
-  <si>
-    <t>0.9645,0.0335,0.0015,0.0003</t>
-  </si>
-  <si>
-    <t>0.9868,0.0114,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.9542,0.0021,0.0683,0.0003</t>
-  </si>
-  <si>
-    <t>0.8304,0.0011,0.3977,0.0002</t>
-  </si>
-  <si>
-    <t>0.9397,0.0062,0.0758,0.0019</t>
-  </si>
-  <si>
-    <t>0.9951,0.0002,0.0017,0.0004</t>
-  </si>
-  <si>
-    <t>0.9873,0.0007,0.0186,0.0000</t>
-  </si>
-  <si>
-    <t>0.3308,0.1525,0.1353,0.0002</t>
-  </si>
-  <si>
-    <t>0.9749,0.0017,0.0337,0.0001</t>
-  </si>
-  <si>
-    <t>0.7829,0.2791,0.0117,0.0010</t>
-  </si>
-  <si>
-    <t>0.9703,0.0441,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.9542,0.0332,0.0060,0.0001</t>
-  </si>
-  <si>
-    <t>0.9288,0.0876,0.0024,0.0001</t>
-  </si>
-  <si>
-    <t>0.1124,0.1204,0.7988,0.0017</t>
-  </si>
-  <si>
-    <t>0.0332,0.0098,0.9695,0.0006</t>
-  </si>
-  <si>
-    <t>0.9851,0.0032,0.0128,0.0001</t>
-  </si>
-  <si>
-    <t>0.6468,0.0117,0.5416,0.0024</t>
-  </si>
-  <si>
-    <t>0.0211,0.0041,0.9850,0.0002</t>
-  </si>
-  <si>
-    <t>0.5436,0.0090,0.6422,0.0009</t>
-  </si>
-  <si>
-    <t>0.9318,0.0499,0.0012,0.0012</t>
-  </si>
-  <si>
-    <t>0.9459,0.0571,0.0019,0.0005</t>
-  </si>
-  <si>
-    <t>0.9720,0.0200,0.0006,0.0005</t>
-  </si>
-  <si>
-    <t>0.3770,0.1659,0.6369,0.0067</t>
-  </si>
-  <si>
-    <t>0.9698,0.0242,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.9487,0.0507,0.0013,0.0007</t>
-  </si>
-  <si>
-    <t>0.8589,0.1917,0.0071,0.0008</t>
-  </si>
-  <si>
-    <t>0.1586,0.0175,0.9061,0.0002</t>
-  </si>
-  <si>
-    <t>0.0728,0.0071,0.9662,0.0005</t>
-  </si>
-  <si>
-    <t>0.5899,0.0061,0.5795,0.0018</t>
-  </si>
-  <si>
-    <t>0.3727,0.4544,0.0570,0.0002</t>
-  </si>
-  <si>
-    <t>0.4772,0.0022,0.7802,0.0002</t>
-  </si>
-  <si>
-    <t>0.9097,0.1356,0.0018,0.0000</t>
-  </si>
-  <si>
-    <t>0.1586,0.9279,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9656,0.0224,0.0053,0.0006</t>
-  </si>
-  <si>
-    <t>0.9479,0.0412,0.0069,0.0003</t>
-  </si>
-  <si>
-    <t>0.0893,0.4952,0.7937,0.0054</t>
-  </si>
-  <si>
-    <t>0.8971,0.0156,0.1124,0.0003</t>
-  </si>
-  <si>
-    <t>0.9220,0.0058,0.1304,0.0002</t>
-  </si>
-  <si>
-    <t>0.6154,0.3708,0.0098,0.0001</t>
-  </si>
-  <si>
-    <t>0.2956,0.0226,0.6869,0.0012</t>
-  </si>
-  <si>
-    <t>0.9480,0.0180,0.0055,0.0031</t>
-  </si>
-  <si>
-    <t>0.9236,0.0377,0.0023,0.0066</t>
-  </si>
-  <si>
-    <t>0.8925,0.0202,0.0300,0.0172</t>
-  </si>
-  <si>
-    <t>0.9789,0.0060,0.0070,0.0011</t>
-  </si>
-  <si>
-    <t>0.9675,0.0102,0.0029,0.0053</t>
-  </si>
-  <si>
-    <t>0.9948,0.0011,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.9536,0.0115,0.0267,0.0003</t>
-  </si>
-  <si>
-    <t>0.8482,0.0362,0.0872,0.0010</t>
-  </si>
-  <si>
-    <t>0.5958,0.0143,0.5401,0.0021</t>
-  </si>
-  <si>
-    <t>0.9609,0.0030,0.0641,0.0004</t>
-  </si>
-  <si>
-    <t>0.5455,0.1563,0.1216,0.0001</t>
-  </si>
-  <si>
-    <t>0.9548,0.0101,0.0380,0.0001</t>
-  </si>
-  <si>
-    <t>0.9709,0.0235,0.0022,0.0006</t>
-  </si>
-  <si>
-    <t>0.9738,0.0241,0.0006,0.0005</t>
-  </si>
-  <si>
-    <t>0.8140,0.2533,0.0049,0.0011</t>
-  </si>
-  <si>
-    <t>0.9697,0.0226,0.0005,0.0005</t>
-  </si>
-  <si>
-    <t>0.8918,0.1502,0.0033,0.0009</t>
-  </si>
-  <si>
-    <t>0.9748,0.0188,0.0008,0.0007</t>
-  </si>
-  <si>
-    <t>0.9268,0.0729,0.0022,0.0007</t>
-  </si>
-  <si>
-    <t>0.8571,0.2124,0.0024,0.0007</t>
-  </si>
-  <si>
-    <t>0.9582,0.0428,0.0008,0.0006</t>
-  </si>
-  <si>
-    <t>0.9474,0.0466,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.9781,0.0176,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.9897,0.0037,0.0003,0.0008</t>
-  </si>
-  <si>
-    <t>0.9473,0.0526,0.0013,0.0006</t>
-  </si>
-  <si>
-    <t>0.9635,0.0245,0.0010,0.0009</t>
-  </si>
-  <si>
-    <t>0.9543,0.0282,0.0015,0.0019</t>
-  </si>
-  <si>
-    <t>0.9668,0.0211,0.0011,0.0012</t>
-  </si>
-  <si>
-    <t>0.7804,0.0274,0.3443,0.0011</t>
-  </si>
-  <si>
-    <t>0.2687,0.0148,0.8266,0.0024</t>
-  </si>
-  <si>
-    <t>0.9897,0.0017,0.0029,0.0003</t>
-  </si>
-  <si>
-    <t>0.9211,0.0058,0.1329,0.0018</t>
-  </si>
-  <si>
-    <t>0.3930,0.7594,0.0131,0.0005</t>
-  </si>
-  <si>
-    <t>0.9275,0.1107,0.0017,0.0002</t>
-  </si>
-  <si>
-    <t>0.6470,0.4656,0.0113,0.0005</t>
-  </si>
-  <si>
-    <t>0.8961,0.1553,0.0029,0.0004</t>
-  </si>
-  <si>
-    <t>0.7280,0.4083,0.0086,0.0005</t>
-  </si>
-  <si>
-    <t>0.2906,0.8393,0.0036,0.0004</t>
-  </si>
-  <si>
-    <t>0.5818,0.5802,0.0120,0.0010</t>
-  </si>
-  <si>
-    <t>0.8758,0.1042,0.0189,0.0011</t>
-  </si>
-  <si>
-    <t>0.9615,0.0144,0.0157,0.0008</t>
-  </si>
-  <si>
-    <t>0.9818,0.0088,0.0030,0.0002</t>
-  </si>
-  <si>
-    <t>0.9716,0.0147,0.0048,0.0003</t>
-  </si>
-  <si>
-    <t>0.9719,0.0114,0.0111,0.0006</t>
-  </si>
-  <si>
-    <t>0.9227,0.1275,0.0024,0.0001</t>
-  </si>
-  <si>
-    <t>0.9365,0.0714,0.0033,0.0000</t>
-  </si>
-  <si>
-    <t>0.5741,0.5399,0.0097,0.0006</t>
-  </si>
-  <si>
-    <t>0.5251,0.3184,0.0307,0.0001</t>
-  </si>
-  <si>
-    <t>0.8925,0.1688,0.0025,0.0001</t>
-  </si>
-  <si>
-    <t>0.8624,0.2117,0.0032,0.0004</t>
-  </si>
-  <si>
-    <t>0.7426,0.3353,0.0077,0.0010</t>
-  </si>
-  <si>
-    <t>0.9894,0.0082,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.9070,0.1457,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.9529,0.0599,0.0014,0.0005</t>
-  </si>
-  <si>
-    <t>0.9422,0.0674,0.0016,0.0003</t>
-  </si>
-  <si>
-    <t>0.9708,0.0144,0.0008,0.0015</t>
-  </si>
-  <si>
-    <t>0.9629,0.0340,0.0040,0.0009</t>
-  </si>
-  <si>
-    <t>0.9092,0.0566,0.0040,0.0025</t>
-  </si>
-  <si>
-    <t>0.7184,0.3946,0.0076,0.0014</t>
-  </si>
-  <si>
-    <t>0.4573,0.0191,0.6872,0.0010</t>
-  </si>
-  <si>
-    <t>0.3010,0.0759,0.7667,0.0007</t>
-  </si>
-  <si>
-    <t>0.7730,0.0016,0.4303,0.0004</t>
-  </si>
-  <si>
-    <t>0.9916,0.0012,0.0103,0.0001</t>
-  </si>
-  <si>
-    <t>0.9501,0.0238,0.0218,0.0004</t>
-  </si>
-  <si>
-    <t>0.9742,0.0151,0.0051,0.0003</t>
-  </si>
-  <si>
-    <t>0.9706,0.0126,0.0080,0.0003</t>
-  </si>
-  <si>
-    <t>0.9827,0.0078,0.0027,0.0001</t>
-  </si>
-  <si>
-    <t>0.9869,0.0021,0.0020,0.0015</t>
-  </si>
-  <si>
-    <t>0.9552,0.0133,0.0067,0.0080</t>
-  </si>
-  <si>
-    <t>0.9691,0.0046,0.0053,0.0057</t>
-  </si>
-  <si>
-    <t>0.9774,0.0076,0.0022,0.0013</t>
-  </si>
-  <si>
-    <t>0.8236,0.0453,0.0463,0.0003</t>
-  </si>
-  <si>
-    <t>0.9375,0.0570,0.0028,0.0013</t>
-  </si>
-  <si>
-    <t>0.8334,0.2548,0.0059,0.0007</t>
-  </si>
-  <si>
-    <t>0.8920,0.1315,0.0019,0.0004</t>
-  </si>
-  <si>
-    <t>0.6264,0.5517,0.0061,0.0005</t>
-  </si>
-  <si>
-    <t>0.9240,0.0764,0.0041,0.0008</t>
-  </si>
-  <si>
-    <t>0.9787,0.0111,0.0025,0.0007</t>
-  </si>
-  <si>
-    <t>0.8605,0.1385,0.0076,0.0025</t>
-  </si>
-  <si>
-    <t>0.2392,0.2142,0.7716,0.0090</t>
-  </si>
-  <si>
-    <t>0.9707,0.0128,0.0009,0.0012</t>
-  </si>
-  <si>
-    <t>0.9376,0.0493,0.0045,0.0017</t>
-  </si>
-  <si>
-    <t>0.9632,0.0343,0.0027,0.0004</t>
-  </si>
-  <si>
-    <t>0.9021,0.1154,0.0057,0.0003</t>
-  </si>
-  <si>
-    <t>0.9355,0.0797,0.0037,0.0002</t>
-  </si>
-  <si>
-    <t>0.8058,0.1949,0.0206,0.0010</t>
-  </si>
-  <si>
-    <t>0.9851,0.0091,0.0014,0.0002</t>
-  </si>
-  <si>
-    <t>0.9555,0.0584,0.0019,0.0002</t>
-  </si>
-  <si>
-    <t>0.9763,0.0135,0.0007,0.0007</t>
-  </si>
-  <si>
-    <t>0.9652,0.0356,0.0007,0.0005</t>
-  </si>
-  <si>
-    <t>0.9621,0.0285,0.0008,0.0008</t>
-  </si>
-  <si>
-    <t>0.9367,0.0519,0.0033,0.0016</t>
-  </si>
-  <si>
-    <t>0.9410,0.0579,0.0028,0.0011</t>
-  </si>
-  <si>
-    <t>0.9216,0.0819,0.0020,0.0006</t>
-  </si>
-  <si>
-    <t>0.9200,0.1000,0.0022,0.0006</t>
-  </si>
-  <si>
-    <t>0.9650,0.0336,0.0020,0.0005</t>
-  </si>
-  <si>
-    <t>0.8701,0.1538,0.0053,0.0009</t>
-  </si>
-  <si>
-    <t>0.7835,0.2735,0.0115,0.0006</t>
-  </si>
-  <si>
-    <t>0.5731,0.5683,0.0053,0.0003</t>
-  </si>
-  <si>
-    <t>0.4111,0.4123,0.1936,0.0020</t>
-  </si>
-  <si>
-    <t>0.9169,0.0997,0.0049,0.0008</t>
-  </si>
-  <si>
-    <t>0.7193,0.4033,0.0110,0.0009</t>
-  </si>
-  <si>
-    <t>0.9417,0.0647,0.0017,0.0004</t>
-  </si>
-  <si>
-    <t>0.8590,0.2520,0.0023,0.0003</t>
-  </si>
-  <si>
-    <t>0.0226,0.3220,0.9229,0.0011</t>
-  </si>
-  <si>
-    <t>0.9401,0.0599,0.0006,0.0005</t>
-  </si>
-  <si>
-    <t>0.7540,0.0017,0.4460,0.0007</t>
-  </si>
-  <si>
-    <t>0.9210,0.0056,0.1290,0.0007</t>
-  </si>
-  <si>
-    <t>0.9329,0.0187,0.0423,0.0016</t>
-  </si>
-  <si>
-    <t>0.2457,0.0269,0.8153,0.0005</t>
-  </si>
-  <si>
-    <t>0.8130,0.0078,0.2969,0.0011</t>
-  </si>
-  <si>
-    <t>0.6120,0.0109,0.5813,0.0011</t>
-  </si>
-  <si>
-    <t>0.7542,0.0066,0.4025,0.0014</t>
-  </si>
-  <si>
-    <t>0.9801,0.0053,0.0054,0.0002</t>
-  </si>
-  <si>
-    <t>0.9778,0.0108,0.0047,0.0002</t>
-  </si>
-  <si>
-    <t>0.9157,0.0345,0.0275,0.0021</t>
-  </si>
-  <si>
-    <t>0.9813,0.0075,0.0058,0.0002</t>
-  </si>
-  <si>
-    <t>0.7658,0.2120,0.0246,0.0007</t>
-  </si>
-  <si>
-    <t>0.8876,0.0834,0.0236,0.0006</t>
-  </si>
-  <si>
-    <t>0.9804,0.0047,0.0100,0.0005</t>
-  </si>
-  <si>
-    <t>0.9931,0.0028,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.7949,0.3428,0.0041,0.0003</t>
-  </si>
-  <si>
-    <t>0.8730,0.1800,0.0041,0.0006</t>
-  </si>
-  <si>
-    <t>0.8815,0.1707,0.0053,0.0005</t>
-  </si>
-  <si>
-    <t>0.7433,0.4422,0.0036,0.0003</t>
-  </si>
-  <si>
-    <t>0.9594,0.0333,0.0007,0.0006</t>
-  </si>
-  <si>
-    <t>0.9086,0.0720,0.0113,0.0007</t>
-  </si>
-  <si>
-    <t>0.9910,0.0030,0.0019,0.0001</t>
-  </si>
-  <si>
-    <t>0.9743,0.0054,0.0137,0.0007</t>
-  </si>
-  <si>
-    <t>0.9863,0.0041,0.0035,0.0002</t>
-  </si>
-  <si>
-    <t>0.9601,0.0151,0.0148,0.0008</t>
-  </si>
-  <si>
-    <t>0.9295,0.0245,0.0380,0.0011</t>
-  </si>
-  <si>
-    <t>0.9714,0.0029,0.0318,0.0004</t>
-  </si>
-  <si>
-    <t>0.9851,0.0016,0.0161,0.0001</t>
-  </si>
-  <si>
-    <t>0.9388,0.0022,0.1362,0.0005</t>
-  </si>
-  <si>
-    <t>0.9884,0.0021,0.0060,0.0001</t>
-  </si>
-  <si>
-    <t>0.9884,0.0060,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9403,0.0707,0.0013,0.0004</t>
-  </si>
-  <si>
-    <t>0.9546,0.0428,0.0016,0.0009</t>
-  </si>
-  <si>
-    <t>0.7852,0.2793,0.0030,0.0010</t>
-  </si>
-  <si>
-    <t>0.9463,0.0368,0.0021,0.0014</t>
-  </si>
-  <si>
-    <t>0.6458,0.4581,0.0155,0.0026</t>
-  </si>
-  <si>
-    <t>0.9118,0.1254,0.0018,0.0007</t>
-  </si>
-  <si>
-    <t>0.7109,0.3336,0.0049,0.0015</t>
-  </si>
-  <si>
-    <t>0.8997,0.1061,0.0137,0.0005</t>
-  </si>
-  <si>
-    <t>0.8727,0.1354,0.0101,0.0006</t>
-  </si>
-  <si>
-    <t>0.7673,0.2912,0.0244,0.0011</t>
-  </si>
-  <si>
-    <t>0.7651,0.0026,0.3875,0.0013</t>
-  </si>
-  <si>
-    <t>0.0820,0.0650,0.8782,0.0015</t>
-  </si>
-  <si>
-    <t>0.6674,0.0546,0.2980,0.0022</t>
-  </si>
-  <si>
-    <t>0.0372,0.0115,0.9806,0.0005</t>
-  </si>
-  <si>
-    <t>0.9223,0.0059,0.1025,0.0004</t>
-  </si>
-  <si>
-    <t>0.1249,0.0135,0.8335,0.0026</t>
-  </si>
-  <si>
-    <t>0.7103,0.0383,0.3220,0.0030</t>
-  </si>
-  <si>
-    <t>0.9321,0.0342,0.0208,0.0006</t>
-  </si>
-  <si>
-    <t>0.9669,0.0099,0.0217,0.0006</t>
-  </si>
-  <si>
-    <t>0.9702,0.0049,0.0226,0.0008</t>
-  </si>
-  <si>
-    <t>0.9936,0.0028,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.9463,0.0580,0.0012,0.0004</t>
-  </si>
-  <si>
-    <t>0.8528,0.1516,0.0055,0.0017</t>
-  </si>
-  <si>
-    <t>0.8103,0.1936,0.0050,0.0015</t>
-  </si>
-  <si>
-    <t>0.9237,0.0688,0.0013,0.0010</t>
-  </si>
-  <si>
-    <t>0.9215,0.0766,0.0038,0.0019</t>
-  </si>
-  <si>
-    <t>0.9623,0.0349,0.0009,0.0004</t>
-  </si>
-  <si>
-    <t>0.9687,0.0181,0.0006,0.0008</t>
-  </si>
-  <si>
-    <t>0.7903,0.3401,0.0039,0.0005</t>
-  </si>
-  <si>
-    <t>0.8174,0.0295,0.1919,0.0011</t>
-  </si>
-  <si>
-    <t>0.3637,0.0679,0.4016,0.0007</t>
-  </si>
-  <si>
-    <t>0.7413,0.0123,0.3661,0.0015</t>
-  </si>
-  <si>
-    <t>0.9675,0.0024,0.0406,0.0004</t>
-  </si>
-  <si>
-    <t>0.6968,0.0020,0.5090,0.0002</t>
-  </si>
-  <si>
-    <t>0.9852,0.0018,0.0096,0.0004</t>
-  </si>
-  <si>
-    <t>0.9711,0.0047,0.0255,0.0002</t>
-  </si>
-  <si>
-    <t>0.9936,0.0011,0.0034,0.0001</t>
-  </si>
-  <si>
-    <t>0.9765,0.0137,0.0009,0.0005</t>
-  </si>
-  <si>
-    <t>0.9866,0.0033,0.0044,0.0009</t>
-  </si>
-  <si>
-    <t>0.9735,0.0068,0.0033,0.0031</t>
-  </si>
-  <si>
-    <t>0.9819,0.0018,0.0032,0.0035</t>
-  </si>
-  <si>
-    <t>0.9701,0.0038,0.0031,0.0114</t>
-  </si>
-  <si>
-    <t>0.9692,0.0132,0.0063,0.0009</t>
+    <t>0.9600,0.0105,0.0146,0.0044</t>
+  </si>
+  <si>
+    <t>0.0659,0.0067,0.0009,0.9729</t>
+  </si>
+  <si>
+    <t>0.9349,0.0050,0.0005,0.0317</t>
+  </si>
+  <si>
+    <t>0.6498,0.0012,0.0008,0.6451</t>
+  </si>
+  <si>
+    <t>0.9990,0.0004,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9964,0.0021,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9979,0.0007,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9931,0.0045,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9928,0.0066,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9987,0.0005,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9982,0.0007,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9629,0.0044,0.0343,0.0003</t>
+  </si>
+  <si>
+    <t>0.5324,0.0088,0.6420,0.0027</t>
+  </si>
+  <si>
+    <t>0.0139,0.0034,0.9867,0.0004</t>
+  </si>
+  <si>
+    <t>0.6412,0.0058,0.5624,0.0017</t>
+  </si>
+  <si>
+    <t>0.9911,0.0015,0.0052,0.0003</t>
+  </si>
+  <si>
+    <t>0.0012,0.9984,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0059,0.9886,0.0038,0.0023</t>
+  </si>
+  <si>
+    <t>0.0745,0.9443,0.0103,0.0011</t>
+  </si>
+  <si>
+    <t>0.0144,0.9884,0.0018,0.0005</t>
+  </si>
+  <si>
+    <t>0.0007,0.9984,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.9521,0.0043,0.0550,0.0027</t>
+  </si>
+  <si>
+    <t>0.6229,0.0082,0.5015,0.0043</t>
+  </si>
+  <si>
+    <t>0.0027,0.0018,0.9949,0.0011</t>
+  </si>
+  <si>
+    <t>0.0716,0.0056,0.9260,0.0022</t>
+  </si>
+  <si>
+    <t>0.0248,0.0036,0.9763,0.0022</t>
+  </si>
+  <si>
+    <t>0.1353,0.0064,0.9149,0.0029</t>
+  </si>
+  <si>
+    <t>0.0043,0.0013,0.9930,0.0015</t>
+  </si>
+  <si>
+    <t>0.6050,0.5838,0.0029,0.0027</t>
+  </si>
+  <si>
+    <t>0.4150,0.4580,0.2280,0.0099</t>
+  </si>
+  <si>
+    <t>0.0014,0.0112,0.9965,0.0020</t>
+  </si>
+  <si>
+    <t>0.0155,0.9432,0.0575,0.0002</t>
+  </si>
+  <si>
+    <t>0.9276,0.0561,0.0230,0.0054</t>
+  </si>
+  <si>
+    <t>0.8820,0.1716,0.0081,0.0017</t>
+  </si>
+  <si>
+    <t>0.4133,0.7862,0.0034,0.0003</t>
+  </si>
+  <si>
+    <t>0.0079,0.9847,0.0693,0.0006</t>
+  </si>
+  <si>
+    <t>0.0138,0.0296,0.9696,0.0059</t>
+  </si>
+  <si>
+    <t>0.1840,0.0021,0.8800,0.0031</t>
+  </si>
+  <si>
+    <t>0.0173,0.0404,0.9795,0.0019</t>
+  </si>
+  <si>
+    <t>0.0060,0.0012,0.9806,0.0163</t>
+  </si>
+  <si>
+    <t>0.0093,0.2255,0.9690,0.0010</t>
+  </si>
+  <si>
+    <t>0.0073,0.8609,0.0507,0.0008</t>
+  </si>
+  <si>
+    <t>0.0257,0.0030,0.9801,0.0011</t>
+  </si>
+  <si>
+    <t>0.7076,0.1774,0.0106,0.0894</t>
+  </si>
+  <si>
+    <t>0.0004,0.9976,0.0005,0.0017</t>
+  </si>
+  <si>
+    <t>0.0111,0.9294,0.0914,0.0037</t>
+  </si>
+  <si>
+    <t>0.0045,0.9884,0.0168,0.0025</t>
+  </si>
+  <si>
+    <t>0.0007,0.0015,0.9943,0.0101</t>
+  </si>
+  <si>
+    <t>0.0005,0.0021,0.9987,0.0003</t>
+  </si>
+  <si>
+    <t>0.0301,0.0116,0.9608,0.0046</t>
+  </si>
+  <si>
+    <t>0.3007,0.0011,0.9032,0.0001</t>
+  </si>
+  <si>
+    <t>0.0029,0.0033,0.9961,0.0008</t>
+  </si>
+  <si>
+    <t>0.0047,0.0086,0.9851,0.0060</t>
+  </si>
+  <si>
+    <t>0.9539,0.0831,0.0020,0.0007</t>
+  </si>
+  <si>
+    <t>0.9817,0.0081,0.0063,0.0013</t>
+  </si>
+  <si>
+    <t>0.9983,0.0005,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.0189,0.0349,0.9857,0.0011</t>
+  </si>
+  <si>
+    <t>0.9952,0.0023,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.9931,0.0054,0.0012,0.0004</t>
+  </si>
+  <si>
+    <t>0.9965,0.0018,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.9716,0.9931,0.0001</t>
+  </si>
+  <si>
+    <t>0.0055,0.0076,0.9957,0.0005</t>
+  </si>
+  <si>
+    <t>0.0023,0.0606,0.9919,0.0029</t>
+  </si>
+  <si>
+    <t>0.0051,0.9391,0.7615,0.0012</t>
+  </si>
+  <si>
+    <t>0.0003,0.0067,0.9977,0.0054</t>
+  </si>
+  <si>
+    <t>0.0072,0.9900,0.0027,0.0004</t>
+  </si>
+  <si>
+    <t>0.0027,0.9971,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.7793,0.0245,0.3065,0.0020</t>
+  </si>
+  <si>
+    <t>0.7077,0.0689,0.3385,0.0058</t>
+  </si>
+  <si>
+    <t>0.0034,0.0141,0.9953,0.0021</t>
+  </si>
+  <si>
+    <t>0.0009,0.9480,0.9715,0.0002</t>
+  </si>
+  <si>
+    <t>0.0008,0.9714,0.9599,0.0002</t>
+  </si>
+  <si>
+    <t>0.0026,0.9901,0.0401,0.0012</t>
+  </si>
+  <si>
+    <t>0.0041,0.9683,0.4835,0.0013</t>
+  </si>
+  <si>
+    <t>0.0101,0.0008,0.0106,0.9867</t>
+  </si>
+  <si>
+    <t>0.0025,0.0081,0.0018,0.9966</t>
+  </si>
+  <si>
+    <t>0.0121,0.0035,0.0004,0.9954</t>
+  </si>
+  <si>
+    <t>0.0766,0.0008,0.0006,0.9839</t>
+  </si>
+  <si>
+    <t>0.0030,0.0004,0.0010,0.9979</t>
+  </si>
+  <si>
+    <t>0.0294,0.0607,0.0070,0.9738</t>
+  </si>
+  <si>
+    <t>0.0015,0.9807,0.5878,0.0004</t>
+  </si>
+  <si>
+    <t>0.0010,0.6200,0.9963,0.0002</t>
+  </si>
+  <si>
+    <t>0.0155,0.7454,0.7346,0.0015</t>
+  </si>
+  <si>
+    <t>0.0016,0.5472,0.9841,0.0007</t>
+  </si>
+  <si>
+    <t>0.0020,0.8916,0.8944,0.0002</t>
+  </si>
+  <si>
+    <t>0.0164,0.6819,0.3896,0.0004</t>
+  </si>
+  <si>
+    <t>0.9949,0.0028,0.0008,0.0006</t>
+  </si>
+  <si>
+    <t>0.9868,0.0194,0.0010,0.0005</t>
+  </si>
+  <si>
+    <t>0.9852,0.0155,0.0008,0.0008</t>
+  </si>
+  <si>
+    <t>0.9957,0.0021,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9921,0.0047,0.0015,0.0007</t>
+  </si>
+  <si>
+    <t>0.9989,0.0002,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9876,0.0054,0.0036,0.0012</t>
+  </si>
+  <si>
+    <t>0.9924,0.0085,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9986,0.0003,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9984,0.0006,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9961,0.0004,0.0004,0.0024</t>
+  </si>
+  <si>
+    <t>0.9954,0.0036,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9957,0.0027,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.0194,0.0038,0.9911,0.0001</t>
+  </si>
+  <si>
+    <t>0.0640,0.0010,0.9692,0.0008</t>
+  </si>
+  <si>
+    <t>0.9128,0.0018,0.1513,0.0024</t>
+  </si>
+  <si>
+    <t>0.0123,0.0015,0.9894,0.0010</t>
+  </si>
+  <si>
+    <t>0.0027,0.9959,0.0013,0.0002</t>
+  </si>
+  <si>
+    <t>0.0011,0.9975,0.0013,0.0002</t>
+  </si>
+  <si>
+    <t>0.0127,0.9809,0.0028,0.0035</t>
+  </si>
+  <si>
+    <t>0.0535,0.9604,0.0062,0.0009</t>
+  </si>
+  <si>
+    <t>0.0010,0.9969,0.0011,0.0005</t>
+  </si>
+  <si>
+    <t>0.0010,0.9969,0.0039,0.0003</t>
+  </si>
+  <si>
+    <t>0.5408,0.6741,0.0032,0.0004</t>
+  </si>
+  <si>
+    <t>0.5935,0.0630,0.3908,0.0089</t>
+  </si>
+  <si>
+    <t>0.1572,0.0019,0.9113,0.0016</t>
+  </si>
+  <si>
+    <t>0.6007,0.0431,0.4177,0.0217</t>
+  </si>
+  <si>
+    <t>0.9388,0.0078,0.0801,0.0016</t>
+  </si>
+  <si>
+    <t>0.0379,0.0366,0.2149,0.8571</t>
+  </si>
+  <si>
+    <t>0.0009,0.9976,0.0039,0.0001</t>
+  </si>
+  <si>
+    <t>0.0019,0.9964,0.0011,0.0004</t>
+  </si>
+  <si>
+    <t>0.0009,0.9964,0.0030,0.0005</t>
+  </si>
+  <si>
+    <t>0.0023,0.6212,0.9391,0.0010</t>
+  </si>
+  <si>
+    <t>0.0111,0.9837,0.0160,0.0005</t>
+  </si>
+  <si>
+    <t>0.7862,0.3518,0.0083,0.0018</t>
+  </si>
+  <si>
+    <t>0.4378,0.6875,0.0181,0.0018</t>
+  </si>
+  <si>
+    <t>0.9955,0.0017,0.0010,0.0008</t>
+  </si>
+  <si>
+    <t>0.9980,0.0004,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9972,0.0005,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.9857,0.0072,0.0055,0.0010</t>
+  </si>
+  <si>
+    <t>0.9983,0.0001,0.0001,0.0014</t>
+  </si>
+  <si>
+    <t>0.9942,0.0024,0.0021,0.0007</t>
+  </si>
+  <si>
+    <t>0.9898,0.0024,0.0011,0.0021</t>
+  </si>
+  <si>
+    <t>0.9952,0.0027,0.0011,0.0005</t>
+  </si>
+  <si>
+    <t>0.0046,0.4816,0.9715,0.0028</t>
+  </si>
+  <si>
+    <t>0.0040,0.2459,0.9799,0.0008</t>
+  </si>
+  <si>
+    <t>0.0231,0.0824,0.8852,0.0157</t>
+  </si>
+  <si>
+    <t>0.2621,0.0224,0.7584,0.0069</t>
+  </si>
+  <si>
+    <t>0.9975,0.0002,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.3446,0.0174,0.6824,0.0152</t>
+  </si>
+  <si>
+    <t>0.6707,0.0137,0.3915,0.0146</t>
+  </si>
+  <si>
+    <t>0.9778,0.0024,0.0225,0.0007</t>
+  </si>
+  <si>
+    <t>0.3948,0.0005,0.0025,0.8188</t>
+  </si>
+  <si>
+    <t>0.0010,0.0037,0.0014,0.9981</t>
+  </si>
+  <si>
+    <t>0.0048,0.0166,0.0012,0.9955</t>
+  </si>
+  <si>
+    <t>0.0937,0.0005,0.0099,0.9412</t>
+  </si>
+  <si>
+    <t>0.0007,0.9965,0.0457,0.0002</t>
+  </si>
+  <si>
+    <t>0.9940,0.0015,0.0016,0.0009</t>
+  </si>
+  <si>
+    <t>0.2303,0.8156,0.0110,0.0045</t>
+  </si>
+  <si>
+    <t>0.9956,0.0008,0.0007,0.0010</t>
+  </si>
+  <si>
+    <t>0.1653,0.8997,0.0025,0.0009</t>
+  </si>
+  <si>
+    <t>0.9967,0.0003,0.0004,0.0011</t>
+  </si>
+  <si>
+    <t>0.5311,0.0071,0.0006,0.5499</t>
+  </si>
+  <si>
+    <t>0.9961,0.0005,0.0012,0.0010</t>
+  </si>
+  <si>
+    <t>0.0046,0.0127,0.9827,0.0386</t>
+  </si>
+  <si>
+    <t>0.9682,0.0006,0.0011,0.0405</t>
+  </si>
+  <si>
+    <t>0.9757,0.0009,0.0003,0.0170</t>
+  </si>
+  <si>
+    <t>0.1644,0.8160,0.0561,0.0030</t>
+  </si>
+  <si>
+    <t>0.9686,0.0185,0.0058,0.0010</t>
+  </si>
+  <si>
+    <t>0.9805,0.0103,0.0068,0.0009</t>
+  </si>
+  <si>
+    <t>0.3053,0.7727,0.0066,0.0098</t>
+  </si>
+  <si>
+    <t>0.9751,0.0119,0.0067,0.0011</t>
+  </si>
+  <si>
+    <t>0.9806,0.0076,0.0089,0.0006</t>
+  </si>
+  <si>
+    <t>0.9978,0.0020,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9969,0.0010,0.0013,0.0002</t>
+  </si>
+  <si>
+    <t>0.9962,0.0028,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9933,0.0006,0.0027,0.0026</t>
+  </si>
+  <si>
+    <t>0.9974,0.0003,0.0012,0.0005</t>
+  </si>
+  <si>
+    <t>0.9941,0.0031,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9972,0.0004,0.0008,0.0006</t>
+  </si>
+  <si>
+    <t>0.9976,0.0002,0.0001,0.0014</t>
+  </si>
+  <si>
+    <t>0.8775,0.1654,0.0035,0.0028</t>
+  </si>
+  <si>
+    <t>0.4638,0.7528,0.0013,0.0002</t>
+  </si>
+  <si>
+    <t>0.9349,0.1409,0.0018,0.0004</t>
+  </si>
+  <si>
+    <t>0.0056,0.7897,0.9742,0.0012</t>
+  </si>
+  <si>
+    <t>0.9523,0.1150,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.8824,0.0688,0.0394,0.0201</t>
+  </si>
+  <si>
+    <t>0.9913,0.0049,0.0021,0.0007</t>
+  </si>
+  <si>
+    <t>0.9720,0.0331,0.0027,0.0013</t>
+  </si>
+  <si>
+    <t>0.0019,0.0837,0.9982,0.0004</t>
+  </si>
+  <si>
+    <t>0.8973,0.0640,0.0480,0.0034</t>
+  </si>
+  <si>
+    <t>0.0030,0.0012,0.9955,0.0004</t>
+  </si>
+  <si>
+    <t>0.0027,0.0273,0.9945,0.0015</t>
+  </si>
+  <si>
+    <t>0.0168,0.0088,0.9779,0.0042</t>
+  </si>
+  <si>
+    <t>0.0069,0.0505,0.9933,0.0013</t>
+  </si>
+  <si>
+    <t>0.0040,0.0092,0.9927,0.0016</t>
+  </si>
+  <si>
+    <t>0.0216,0.0018,0.9823,0.0008</t>
+  </si>
+  <si>
+    <t>0.0008,0.0114,0.9964,0.0040</t>
+  </si>
+  <si>
+    <t>0.2415,0.0078,0.8335,0.0040</t>
+  </si>
+  <si>
+    <t>0.5039,0.0023,0.6779,0.0016</t>
+  </si>
+  <si>
+    <t>0.0603,0.0138,0.9317,0.0044</t>
+  </si>
+  <si>
+    <t>0.0956,0.1473,0.7609,0.0075</t>
+  </si>
+  <si>
+    <t>0.1322,0.2327,0.5170,0.0015</t>
+  </si>
+  <si>
+    <t>0.9324,0.0122,0.0598,0.0013</t>
+  </si>
+  <si>
+    <t>0.7045,0.0656,0.2599,0.0224</t>
+  </si>
+  <si>
+    <t>0.3270,0.0656,0.6871,0.0122</t>
+  </si>
+  <si>
+    <t>0.0097,0.9897,0.0025,0.0007</t>
+  </si>
+  <si>
+    <t>0.0074,0.9935,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.6472,0.6325,0.0007,0.0010</t>
+  </si>
+  <si>
+    <t>0.9855,0.0154,0.0027,0.0007</t>
+  </si>
+  <si>
+    <t>0.6989,0.5097,0.0013,0.0011</t>
+  </si>
+  <si>
+    <t>0.5164,0.0700,0.4764,0.0028</t>
+  </si>
+  <si>
+    <t>0.9563,0.0053,0.0399,0.0029</t>
+  </si>
+  <si>
+    <t>0.9334,0.0130,0.0120,0.0115</t>
+  </si>
+  <si>
+    <t>0.5891,0.0185,0.5688,0.0066</t>
+  </si>
+  <si>
+    <t>0.8358,0.0057,0.1520,0.0193</t>
+  </si>
+  <si>
+    <t>0.0240,0.0014,0.9753,0.0037</t>
+  </si>
+  <si>
+    <t>0.1466,0.0363,0.8626,0.0060</t>
+  </si>
+  <si>
+    <t>0.1637,0.1435,0.7226,0.0066</t>
+  </si>
+  <si>
+    <t>0.0347,0.0168,0.9560,0.0039</t>
+  </si>
+  <si>
+    <t>0.0439,0.1199,0.7985,0.0019</t>
+  </si>
+  <si>
+    <t>0.9978,0.0010,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9954,0.0017,0.0011,0.0008</t>
+  </si>
+  <si>
+    <t>0.9931,0.0040,0.0006,0.0007</t>
+  </si>
+  <si>
+    <t>0.9979,0.0021,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9773,0.0296,0.0005,0.0019</t>
+  </si>
+  <si>
+    <t>0.9962,0.0028,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9954,0.0018,0.0006,0.0011</t>
+  </si>
+  <si>
+    <t>0.9968,0.0015,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.0009,0.0822,0.9982,0.0002</t>
+  </si>
+  <si>
+    <t>0.1185,0.2372,0.6607,0.0126</t>
+  </si>
+  <si>
+    <t>0.9798,0.0042,0.0146,0.0010</t>
+  </si>
+  <si>
+    <t>0.0039,0.0062,0.9963,0.0003</t>
+  </si>
+  <si>
+    <t>0.0003,0.0005,0.9978,0.0019</t>
+  </si>
+  <si>
+    <t>0.0002,0.0033,0.9987,0.0007</t>
+  </si>
+  <si>
+    <t>0.0056,0.0041,0.9971,0.0001</t>
+  </si>
+  <si>
+    <t>0.0820,0.0241,0.8863,0.0016</t>
+  </si>
+  <si>
+    <t>0.0032,0.0044,0.9967,0.0004</t>
+  </si>
+  <si>
+    <t>0.0378,0.0322,0.9481,0.0057</t>
+  </si>
+  <si>
+    <t>0.0089,0.0138,0.9785,0.0042</t>
+  </si>
+  <si>
+    <t>0.9586,0.0007,0.0543,0.0022</t>
+  </si>
+  <si>
+    <t>0.7511,0.0010,0.3570,0.0027</t>
+  </si>
+  <si>
+    <t>0.9912,0.0008,0.0054,0.0005</t>
+  </si>
+  <si>
+    <t>0.9941,0.0067,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9973,0.0030,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9979,0.0008,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9893,0.0091,0.0021,0.0009</t>
+  </si>
+  <si>
+    <t>0.9988,0.0002,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9957,0.0029,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9979,0.0014,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9973,0.0013,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.0104,0.0305,0.9718,0.0012</t>
+  </si>
+  <si>
+    <t>0.0094,0.0695,0.9793,0.0007</t>
+  </si>
+  <si>
+    <t>0.0169,0.0835,0.9405,0.0059</t>
+  </si>
+  <si>
+    <t>0.0704,0.0100,0.9168,0.0046</t>
+  </si>
+  <si>
+    <t>0.0023,0.0009,0.9976,0.0002</t>
+  </si>
+  <si>
+    <t>0.0130,0.0172,0.9498,0.0905</t>
+  </si>
+  <si>
+    <t>0.2585,0.0073,0.8036,0.0072</t>
+  </si>
+  <si>
+    <t>0.0103,0.0043,0.9712,0.0176</t>
+  </si>
+  <si>
+    <t>0.9498,0.0007,0.0010,0.0849</t>
+  </si>
+  <si>
+    <t>0.0134,0.0038,0.0057,0.9906</t>
+  </si>
+  <si>
+    <t>0.1461,0.0040,0.0003,0.9516</t>
+  </si>
+  <si>
+    <t>0.0055,0.0006,0.0026,0.9958</t>
+  </si>
+  <si>
+    <t>0.0030,0.0007,0.0004,0.9985</t>
+  </si>
+  <si>
+    <t>0.9876,0.0014,0.0031,0.0018</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2149,7 +2149,7 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
         <v>278</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2191,7 +2191,7 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
         <v>281</v>
@@ -2205,7 +2205,7 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
         <v>282</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2275,7 +2275,7 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
         <v>287</v>
@@ -2289,7 +2289,7 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
         <v>288</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2317,7 +2317,7 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
         <v>290</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2359,7 +2359,7 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
         <v>293</v>
@@ -2443,7 +2443,7 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
         <v>299</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2485,7 +2485,7 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
         <v>302</v>
@@ -2499,7 +2499,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2513,7 +2513,7 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
         <v>304</v>
@@ -2527,7 +2527,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -2541,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
         <v>306</v>
@@ -2555,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2597,7 +2597,7 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
         <v>310</v>
@@ -2611,7 +2611,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2807,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
         <v>325</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2877,7 +2877,7 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -2975,7 +2975,7 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
         <v>337</v>
@@ -2989,7 +2989,7 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D76" t="s">
         <v>338</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3031,7 +3031,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>341</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3087,7 +3087,7 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
         <v>345</v>
@@ -3101,7 +3101,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
         <v>346</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3143,7 +3143,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3157,7 +3157,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3395,7 +3395,7 @@
         <v>261</v>
       </c>
       <c r="C105" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D105" t="s">
         <v>367</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3465,7 +3465,7 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D110" t="s">
         <v>372</v>
@@ -3479,7 +3479,7 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
         <v>373</v>
@@ -3493,7 +3493,7 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
         <v>374</v>
@@ -3507,7 +3507,7 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D113" t="s">
         <v>375</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3605,7 +3605,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
         <v>382</v>
@@ -3619,7 +3619,7 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
         <v>383</v>
@@ -3633,7 +3633,7 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
         <v>384</v>
@@ -3661,7 +3661,7 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
         <v>386</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3703,7 +3703,7 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
         <v>389</v>
@@ -3857,7 +3857,7 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
         <v>400</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -3899,7 +3899,7 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
         <v>403</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3955,7 +3955,7 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
         <v>407</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4081,7 +4081,7 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
         <v>416</v>
@@ -4151,7 +4151,7 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
         <v>421</v>
@@ -4193,7 +4193,7 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
         <v>424</v>
@@ -4361,7 +4361,7 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
         <v>436</v>
@@ -4375,7 +4375,7 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
         <v>437</v>
@@ -4389,7 +4389,7 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D176" t="s">
         <v>438</v>
@@ -4487,7 +4487,7 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D183" t="s">
         <v>445</v>
@@ -4501,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
         <v>446</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4543,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
         <v>449</v>
@@ -4571,7 +4571,7 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
         <v>451</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4599,7 +4599,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
         <v>453</v>
@@ -4613,7 +4613,7 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
         <v>454</v>
@@ -4627,7 +4627,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
         <v>455</v>
@@ -4641,7 +4641,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
         <v>456</v>
@@ -4683,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
         <v>459</v>
@@ -4697,7 +4697,7 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
         <v>460</v>
@@ -4711,7 +4711,7 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
         <v>461</v>
@@ -4725,7 +4725,7 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
         <v>462</v>
@@ -4753,7 +4753,7 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
         <v>464</v>
@@ -4809,7 +4809,7 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
         <v>468</v>
@@ -4837,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
         <v>470</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -4865,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
         <v>472</v>
@@ -4879,7 +4879,7 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
         <v>473</v>
@@ -4893,7 +4893,7 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
         <v>474</v>
@@ -5019,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
         <v>483</v>
@@ -5033,7 +5033,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
         <v>484</v>
@@ -5061,7 +5061,7 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D224" t="s">
         <v>486</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5145,7 +5145,7 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
         <v>492</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
@@ -5327,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
         <v>505</v>
@@ -5341,7 +5341,7 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D244" t="s">
         <v>506</v>
@@ -5355,7 +5355,7 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
         <v>507</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5397,7 +5397,7 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
         <v>510</v>
@@ -5411,7 +5411,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
         <v>511</v>
@@ -5425,7 +5425,7 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
         <v>512</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5481,7 +5481,7 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>516</v>
@@ -5495,7 +5495,7 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
         <v>517</v>
